--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103711548</v>
+        <v>137433705</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596578</v>
+        <v>596693</v>
       </c>
       <c r="R2" t="n">
-        <v>7072346</v>
+        <v>7072379</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,86 +748,116 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Insänkt bål. Alt. korning nållav, men tycker den här var åt det längre hållet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103711548</t>
+          <t>https://artportalen.se/Sighting/137433705</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135274927</v>
+        <v>137433691</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>81501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596677</v>
+        <v>596587</v>
       </c>
       <c r="R3" t="n">
-        <v>7072385</v>
+        <v>7072283</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,22 +881,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +911,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135274927</t>
+          <t>https://artportalen.se/Sighting/137433691</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135275217</v>
+        <v>103711548</v>
       </c>
       <c r="B4" t="n">
-        <v>80556</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,37 +939,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Kullberg, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596673</v>
+        <v>596578</v>
       </c>
       <c r="R4" t="n">
-        <v>7072364</v>
+        <v>7072346</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,33 +1010,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135275217</t>
+          <t>https://artportalen.se/Sighting/103711548</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135275017</v>
+        <v>137433710</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>92202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,37 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596592</v>
+        <v>596611</v>
       </c>
       <c r="R5" t="n">
-        <v>7072271</v>
+        <v>7072382</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,27 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,68 +1129,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135275017</t>
+          <t>https://artportalen.se/Sighting/137433710</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135274794</v>
+        <v>137433714</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596677</v>
+        <v>596589</v>
       </c>
       <c r="R6" t="n">
-        <v>7072385</v>
+        <v>7072370</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,22 +1211,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,72 +1235,68 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135274794</t>
+          <t>https://artportalen.se/Sighting/137433714</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135275209</v>
+        <v>135274927</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596673</v>
+        <v>596677</v>
       </c>
       <c r="R7" t="n">
-        <v>7072365</v>
+        <v>7072385</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1347,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,7 +1364,3810 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135274927</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137433681</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596580</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072342</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433681</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137433687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596586</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7072310</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433687</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137433698</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596655</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072355</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433698</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137433702</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596680</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7072378</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433702</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137433709</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596642</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7072387</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433709</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137433711</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596590</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433711</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137433708</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7072389</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433708</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137433715</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78935</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>596575</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7072364</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433715</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137433683</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83506</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596583</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7072333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433683</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137433694</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83523</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596554</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7072228</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433694</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137433701</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83523</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>596681</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7072362</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433701</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137433707</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596683</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7072391</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433707</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137433716</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596576</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7072364</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433716</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137433692</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596601</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7072282</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433692</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137433696</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596629</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7072289</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433696</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135275217</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7072364</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275217</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137433682</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596593</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7072333</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433682</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137433690</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>596580</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7072306</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433690</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137433700</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7072358</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433700</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137433703</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>596688</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7072387</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433703</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137433712</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>596583</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7072387</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433712</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137433717</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80651</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>596567</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7072349</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433717</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137433713</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80658</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>596582</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7072384</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433713</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137433697</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78532</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>596620</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7072327</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433697</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137433684</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>596580</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7072334</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433684</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137433699</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>596654</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7072362</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433699</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135275017</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>596592</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7072271</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275017</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137433695</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>596589</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7072227</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433695</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137434218</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>596585</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7072325</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137434218</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135274794</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274794</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135275209</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7072365</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135275209</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137433706</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79290</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>596679</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7072390</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433706</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137433693</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92573</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>596568</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7072260</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433693</t>
         </is>
       </c>
     </row>
@@ -1365,6 +5179,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137433705</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137433691</v>
       </c>
       <c r="B3" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137433710</v>
       </c>
       <c r="B5" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>137433714</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137433681</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>137433687</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>137433698</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137433702</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>137433709</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>137433711</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>137433708</v>
       </c>
       <c r="B14" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>137433715</v>
       </c>
       <c r="B15" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>137433683</v>
       </c>
       <c r="B16" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>137433694</v>
       </c>
       <c r="B17" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137433701</v>
       </c>
       <c r="B18" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137433707</v>
       </c>
       <c r="B19" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137433716</v>
       </c>
       <c r="B20" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137433692</v>
       </c>
       <c r="B21" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137433696</v>
       </c>
       <c r="B22" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137433682</v>
       </c>
       <c r="B24" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>137433690</v>
       </c>
       <c r="B25" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137433700</v>
       </c>
       <c r="B26" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>137433703</v>
       </c>
       <c r="B27" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137433712</v>
       </c>
       <c r="B28" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>137433717</v>
       </c>
       <c r="B29" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137433713</v>
       </c>
       <c r="B30" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,48 +4014,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137433697</v>
+        <v>137433684</v>
       </c>
       <c r="B31" t="n">
-        <v>78532</v>
+        <v>58032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596620</v>
+        <v>596580</v>
       </c>
       <c r="R31" t="n">
-        <v>7072327</v>
+        <v>7072334</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4087,7 +4085,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4097,16 +4095,15 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4124,13 +4121,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433697</t>
+          <t>https://artportalen.se/Sighting/137433684</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137433684</v>
+        <v>137433699</v>
       </c>
       <c r="B32" t="n">
         <v>58032</v>
@@ -4166,10 +4163,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596580</v>
+        <v>596654</v>
       </c>
       <c r="R32" t="n">
-        <v>7072334</v>
+        <v>7072362</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4201,7 +4198,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4211,7 +4208,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4237,33 +4234,33 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433684</t>
+          <t>https://artportalen.se/Sighting/137433699</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137433699</v>
+        <v>135275017</v>
       </c>
       <c r="B33" t="n">
-        <v>58032</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4272,20 +4269,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596654</v>
+        <v>596592</v>
       </c>
       <c r="R33" t="n">
-        <v>7072362</v>
+        <v>7072271</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4309,22 +4305,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4339,27 +4340,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433699</t>
+          <t>https://artportalen.se/Sighting/135275017</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135275017</v>
+        <v>137433695</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4385,19 +4386,20 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596592</v>
+        <v>596589</v>
       </c>
       <c r="R34" t="n">
-        <v>7072271</v>
+        <v>7072227</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4421,27 +4423,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4456,27 +4453,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135275017</t>
+          <t>https://artportalen.se/Sighting/137433695</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137433695</v>
+        <v>137434218</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58139</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,16 +4481,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4501,18 +4498,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596589</v>
+        <v>596585</v>
       </c>
       <c r="R35" t="n">
-        <v>7072227</v>
+        <v>7072325</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4554,7 +4558,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4580,16 +4584,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433695</t>
+          <t>https://artportalen.se/Sighting/137434218</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137434218</v>
+        <v>135274794</v>
       </c>
       <c r="B36" t="n">
-        <v>58139</v>
+        <v>79199</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,45 +4601,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596585</v>
+        <v>596677</v>
       </c>
       <c r="R36" t="n">
-        <v>7072325</v>
+        <v>7072385</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4659,22 +4658,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4683,30 +4682,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137434218</t>
+          <t>https://artportalen.se/Sighting/135274794</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135274794</v>
+        <v>135275209</v>
       </c>
       <c r="B37" t="n">
         <v>79199</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596677</v>
+        <v>596673</v>
       </c>
       <c r="R37" t="n">
-        <v>7072385</v>
+        <v>7072365</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4816,16 +4816,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135274794</t>
+          <t>https://artportalen.se/Sighting/135275209</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135275209</v>
+        <v>137433706</v>
       </c>
       <c r="B38" t="n">
-        <v>79199</v>
+        <v>79291</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4851,22 +4851,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+          <t>Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596673</v>
+        <v>596679</v>
       </c>
       <c r="R38" t="n">
-        <v>7072365</v>
+        <v>7072390</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4890,22 +4887,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4914,34 +4911,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johanna Liljegren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135275209</t>
+          <t>https://artportalen.se/Sighting/137433706</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137433706</v>
+        <v>137433693</v>
       </c>
       <c r="B39" t="n">
-        <v>79290</v>
+        <v>92574</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4949,21 +4945,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6040186</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4973,10 +4969,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596679</v>
+        <v>596568</v>
       </c>
       <c r="R39" t="n">
-        <v>7072390</v>
+        <v>7072260</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5008,7 +5004,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5018,7 +5014,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5027,8 +5023,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5043,129 +5050,6 @@
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137433706</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>137433693</v>
-      </c>
-      <c r="B40" t="n">
-        <v>92573</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Mehållstjärnarna, Ång</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>596568</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7072260</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137433693</t>
         </is>
@@ -5211,7 +5095,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433705</v>
       </c>
       <c r="B2" t="n">
-        <v>83519</v>
+        <v>83521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137433691</v>
       </c>
       <c r="B3" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137433710</v>
       </c>
       <c r="B5" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>137433714</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137433681</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>137433687</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>137433698</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137433702</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>137433709</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>137433711</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>137433708</v>
       </c>
       <c r="B14" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>137433715</v>
       </c>
       <c r="B15" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>137433683</v>
       </c>
       <c r="B16" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>137433694</v>
       </c>
       <c r="B17" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137433701</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137433707</v>
       </c>
       <c r="B19" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137433716</v>
       </c>
       <c r="B20" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137433692</v>
       </c>
       <c r="B21" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137433696</v>
       </c>
       <c r="B22" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137433682</v>
       </c>
       <c r="B24" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>137433690</v>
       </c>
       <c r="B25" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137433700</v>
       </c>
       <c r="B26" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>137433703</v>
       </c>
       <c r="B27" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137433712</v>
       </c>
       <c r="B28" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>137433717</v>
       </c>
       <c r="B29" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137433713</v>
       </c>
       <c r="B30" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137433706</v>
       </c>
       <c r="B38" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>137433693</v>
       </c>
       <c r="B39" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433705</v>
       </c>
       <c r="B2" t="n">
-        <v>83521</v>
+        <v>83525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137433691</v>
       </c>
       <c r="B3" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>137433710</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>137433714</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>137433681</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>137433687</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>137433698</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137433702</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>137433709</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>137433711</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>137433708</v>
       </c>
       <c r="B14" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>137433715</v>
       </c>
       <c r="B15" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>137433683</v>
       </c>
       <c r="B16" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>137433694</v>
       </c>
       <c r="B17" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137433701</v>
       </c>
       <c r="B18" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137433707</v>
       </c>
       <c r="B19" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137433716</v>
       </c>
       <c r="B20" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137433692</v>
       </c>
       <c r="B21" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137433696</v>
       </c>
       <c r="B22" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137433682</v>
       </c>
       <c r="B24" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>137433690</v>
       </c>
       <c r="B25" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>137433700</v>
       </c>
       <c r="B26" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>137433703</v>
       </c>
       <c r="B27" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137433712</v>
       </c>
       <c r="B28" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>137433717</v>
       </c>
       <c r="B29" t="n">
-        <v>80654</v>
+        <v>80658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>137433713</v>
       </c>
       <c r="B30" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137433684</v>
       </c>
       <c r="B31" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>137433699</v>
       </c>
       <c r="B32" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137433695</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>137434218</v>
       </c>
       <c r="B35" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>137433706</v>
       </c>
       <c r="B38" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>137433693</v>
       </c>
       <c r="B39" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
